--- a/data/sites.xlsx
+++ b/data/sites.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>已验证：能稳定打开对应航线的搜索结果页。经停筛选参数尚未确认，模板里没加，打开后可能需要手动点一下"1 stop or fewer"筛选。</t>
+          <t>已验证：能稳定打开对应航线的搜索结果页。经停筛选已确认无法通过 URL 参数带上（点击筛选后地址栏不变），打开后如需筛选经停请手动点一下"1 stop or fewer"。</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>搜索URL模板未验证，留空。留空时程序会打开主页，需要手动输入航线搜索。</t>
+          <t>实测最终跳转到 https://nl.flightnetwork.com/rf/result（白标 flightnetwork.com），地址栏没有看到航线/日期参数，可能是靠服务器端会话记录搜索条件，无法直接拼 URL 打开对应结果。暂时留空，打开首页手动搜索。如果发现完整地址其实带了参数，把模板补进来即可。</t>
         </is>
       </c>
     </row>
@@ -507,10 +507,14 @@
           <t>https://tix.nl</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://tix.nl/flights/search?adults=1&amp;children=0&amp;infants=0&amp;cabinClass=NO_PREFERENCE&amp;bounds[0][departureCode]={origin}&amp;bounds[0][destinationCode]={destination}&amp;bounds[0][departureDate]={date}</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>搜索URL模板未验证，留空。留空时程序会打开主页，需要手动输入航线搜索。</t>
+          <t>已根据实测 URL 配置，未做二次验证（没有反复测试是否每次都稳定生效），建议首次使用留意一下结果是否正确。</t>
         </is>
       </c>
     </row>
@@ -525,10 +529,14 @@
           <t>https://flights.kilroy.net/</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://flights.kilroy.net/search-results?adults=1&amp;children=0&amp;infants=0&amp;cabinClass=ECONOMY&amp;tripType=ONE_WAY&amp;outFrom={origin}&amp;outTo={destination}&amp;outDate={dateDDMMYYYY}</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>搜索URL模板未验证，留空。留空时程序会打开主页，需要手动输入航线搜索。</t>
+          <t>实测 URL 里还带了一个 searchRequestId（随机会话 ID），这里的模板里去掉了，因为没法预先构造出有效值。如果打开后页面提示错误或空结果，说明这个网站强制要求这个 ID，只能退回"打开首页手动搜索"（把这一行的模板列清空即可）。日期格式和其他网站不一样，是"日.月.年"，模板已用 {dateDDMMYYYY} 占位符处理。</t>
         </is>
       </c>
     </row>
@@ -543,10 +551,14 @@
           <t>https://www.connections.be/en/flights</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.connections.be/en/flights/search?adults=1&amp;children=0&amp;infants=0&amp;mode=ONE_WAY&amp;fareType=economy&amp;from={originWithPrefix}&amp;to={destinationWithPrefix}&amp;departure={date}&amp;return=&amp;isDirectFlight=0&amp;stops=0&amp;carriers=all&amp;providers=all&amp;luggage=all</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>搜索URL模板未验证，留空。留空时程序会打开主页，需要手动输入航线搜索。</t>
+          <t>实测 URL 里 from/to 参数带了 A-（具体机场）或 C-（多机场城市，如北京 BJS、东京 TYO）前缀，模板用 {originWithPrefix}/{destinationWithPrefix} 占位符自动处理（哪些代码算"多机场城市"在 lib/buildSearchUrl.js 的 MULTI_AIRPORT_CITY_CODES 里，可以按需编辑）。还去掉了一个 journeyUid 随机 ID，没做二次验证，建议首次使用留意结果是否正确。</t>
         </is>
       </c>
     </row>

--- a/data/sites.xlsx
+++ b/data/sites.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>已根据实测 URL 配置，未做二次验证（没有反复测试是否每次都稳定生效），建议首次使用留意一下结果是否正确。</t>
+          <t>已根据实测 URL 配置。注意：打开后网站需要几秒到二十几秒查询真实结果（查询完成后网站会自己在地址栏加一个 searchId，不用我们提供），刚打开时页面可能显示筛选栏但结果区域是加载动画，属于正常现象，耐心等一下就好，不是链接错了。</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>实测 URL 里还带了一个 searchRequestId（随机会话 ID），这里的模板里去掉了，因为没法预先构造出有效值。如果打开后页面提示错误或空结果，说明这个网站强制要求这个 ID，只能退回"打开首页手动搜索"（把这一行的模板列清空即可）。日期格式和其他网站不一样，是"日.月.年"，模板已用 {dateDDMMYYYY} 占位符处理。</t>
+          <t>已根据实测 URL 配置。同 TIX，打开后需要等待（实测约 20-30 秒）才会出真实结果，等待期间会显示"Searching for flights..."，属于正常现象。日期格式和其他网站不一样，是"日.月.年"，模板已用 {dateDDMMYYYY} 占位符处理。</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>实测 URL 里 from/to 参数带了 A-（具体机场）或 C-（多机场城市，如北京 BJS、东京 TYO）前缀，模板用 {originWithPrefix}/{destinationWithPrefix} 占位符自动处理（哪些代码算"多机场城市"在 lib/buildSearchUrl.js 的 MULTI_AIRPORT_CITY_CODES 里，可以按需编辑）。还去掉了一个 journeyUid 随机 ID，没做二次验证，建议首次使用留意结果是否正确。</t>
+          <t>已根据实测 URL 配置，from/to 参数带了 A-（具体机场）或 C-（多机场城市，如北京 BJS、东京 TYO）前缀，模板用 {originWithPrefix}/{destinationWithPrefix} 占位符自动处理（哪些代码算"多机场城市"在 lib/buildSearchUrl.js 的 MULTI_AIRPORT_CITY_CODES 里，可以按需编辑）。同样可能需要等待才出结果，如果打开后长时间只显示"欢迎搜索"的提示而不是结果，先多等一会/刷新一次再判断是否有问题。</t>
         </is>
       </c>
     </row>
